--- a/outputs/dados/dados_api_bacen.xlsx
+++ b/outputs/dados/dados_api_bacen.xlsx
@@ -596,10 +596,8 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>21473,20789</t>
-        </is>
+      <c r="AA2" t="n">
+        <v>21473.20789</v>
       </c>
     </row>
     <row r="3">
@@ -633,10 +631,8 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>21854,83683</t>
-        </is>
+      <c r="AA3" t="n">
+        <v>21854.83683</v>
       </c>
     </row>
     <row r="4">
@@ -670,10 +666,8 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>22365,59454</t>
-        </is>
+      <c r="AA4" t="n">
+        <v>22365.59454</v>
       </c>
     </row>
     <row r="5">
@@ -707,10 +701,8 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>21952,7115</t>
-        </is>
+      <c r="AA5" t="n">
+        <v>21952.7115</v>
       </c>
     </row>
     <row r="6">
@@ -744,10 +736,8 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>22133,65626</t>
-        </is>
+      <c r="AA6" t="n">
+        <v>22133.65626</v>
       </c>
     </row>
     <row r="7">
@@ -781,10 +771,8 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>22575,32596</t>
-        </is>
+      <c r="AA7" t="n">
+        <v>22575.32596</v>
       </c>
     </row>
     <row r="8">
@@ -818,10 +806,8 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>22480,7412</t>
-        </is>
+      <c r="AA8" t="n">
+        <v>22480.7412</v>
       </c>
     </row>
     <row r="9">
@@ -855,10 +841,8 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>22515,2852</t>
-        </is>
+      <c r="AA9" t="n">
+        <v>22515.2852</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +876,8 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>21409,05475</t>
-        </is>
+      <c r="AA10" t="n">
+        <v>21409.05475</v>
       </c>
     </row>
     <row r="11">
@@ -929,10 +911,8 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>21706,79112</t>
-        </is>
+      <c r="AA11" t="n">
+        <v>21706.79112</v>
       </c>
     </row>
     <row r="12">
@@ -966,10 +946,8 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>22253,73778</t>
-        </is>
+      <c r="AA12" t="n">
+        <v>22253.73778</v>
       </c>
     </row>
     <row r="13">
@@ -1003,10 +981,8 @@
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>22956,9549</t>
-        </is>
+      <c r="AA13" t="n">
+        <v>22956.9549</v>
       </c>
     </row>
     <row r="14">
@@ -1084,10 +1060,8 @@
       <c r="Z14" t="n">
         <v>100</v>
       </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>23016,99567</t>
-        </is>
+      <c r="AA14" t="n">
+        <v>23016.99567</v>
       </c>
     </row>
     <row r="15">
@@ -1165,10 +1139,8 @@
       <c r="Z15" t="n">
         <v>100</v>
       </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>23559,00746</t>
-        </is>
+      <c r="AA15" t="n">
+        <v>23559.00746</v>
       </c>
     </row>
     <row r="16">
@@ -1248,10 +1220,8 @@
       <c r="Z16" t="n">
         <v>100</v>
       </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>23645,36746</t>
-        </is>
+      <c r="AA16" t="n">
+        <v>23645.36746</v>
       </c>
     </row>
     <row r="17">
@@ -1329,10 +1299,8 @@
       <c r="Z17" t="n">
         <v>100</v>
       </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>23892,93279</t>
-        </is>
+      <c r="AA17" t="n">
+        <v>23892.93279</v>
       </c>
     </row>
     <row r="18">
@@ -1410,10 +1378,8 @@
       <c r="Z18" t="n">
         <v>100</v>
       </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>24064,00783</t>
-        </is>
+      <c r="AA18" t="n">
+        <v>24064.00783</v>
       </c>
     </row>
     <row r="19">
@@ -1493,10 +1459,8 @@
       <c r="Z19" t="n">
         <v>100</v>
       </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>19977,12373</t>
-        </is>
+      <c r="AA19" t="n">
+        <v>19977.12373</v>
       </c>
     </row>
     <row r="20">
@@ -1574,10 +1538,8 @@
       <c r="Z20" t="n">
         <v>100.7</v>
       </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>19997,68564</t>
-        </is>
+      <c r="AA20" t="n">
+        <v>19997.68564</v>
       </c>
     </row>
     <row r="21">
@@ -1655,10 +1617,8 @@
       <c r="Z21" t="n">
         <v>101.4049</v>
       </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>20380,95954</t>
-        </is>
+      <c r="AA21" t="n">
+        <v>20380.95954</v>
       </c>
     </row>
     <row r="22">
@@ -1738,10 +1698,8 @@
       <c r="Z22" t="n">
         <v>102.12487479</v>
       </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>21319,40485</t>
-        </is>
+      <c r="AA22" t="n">
+        <v>21319.40485</v>
       </c>
     </row>
     <row r="23">
@@ -1819,10 +1777,8 @@
       <c r="Z23" t="n">
         <v>102.849961401009</v>
       </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>22166,5553</t>
-        </is>
+      <c r="AA23" t="n">
+        <v>22166.5553</v>
       </c>
     </row>
     <row r="24">
@@ -1900,10 +1856,8 @@
       <c r="Z24" t="n">
         <v>103.5801961269562</v>
       </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>22814,66653</t>
-        </is>
+      <c r="AA24" t="n">
+        <v>22814.66653</v>
       </c>
     </row>
     <row r="25">
@@ -1983,10 +1937,8 @@
       <c r="Z25" t="n">
         <v>104.2845414606195</v>
       </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>22335,9854</t>
-        </is>
+      <c r="AA25" t="n">
+        <v>22335.9854</v>
       </c>
     </row>
     <row r="26">
@@ -2064,10 +2016,8 @@
       <c r="Z26" t="n">
         <v>104.6078235391474</v>
       </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>22481,56368</t>
-        </is>
+      <c r="AA26" t="n">
+        <v>22481.56368</v>
       </c>
     </row>
     <row r="27">
@@ -2145,10 +2095,8 @@
       <c r="Z27" t="n">
         <v>105.3400783039214</v>
       </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>23429,05623</t>
-        </is>
+      <c r="AA27" t="n">
+        <v>23429.05623</v>
       </c>
     </row>
     <row r="28">
@@ -2228,10 +2176,8 @@
       <c r="Z28" t="n">
         <v>106.0774588520488</v>
       </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>23364,08061</t>
-        </is>
+      <c r="AA28" t="n">
+        <v>23364.08061</v>
       </c>
     </row>
     <row r="29">
@@ -2309,10 +2255,8 @@
       <c r="Z29" t="n">
         <v>107.223095407651</v>
       </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>23521,99603</t>
-        </is>
+      <c r="AA29" t="n">
+        <v>23521.99603</v>
       </c>
     </row>
     <row r="30">
@@ -2390,10 +2334,8 @@
       <c r="Z30" t="n">
         <v>107.9629347659638</v>
       </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>23711,16555</t>
-        </is>
+      <c r="AA30" t="n">
+        <v>23711.16555</v>
       </c>
     </row>
     <row r="31">
@@ -2473,10 +2415,8 @@
       <c r="Z31" t="n">
         <v>108.7078790158489</v>
       </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>23936,52403</t>
-        </is>
+      <c r="AA31" t="n">
+        <v>23936.52403</v>
       </c>
     </row>
     <row r="32">
@@ -2554,10 +2494,8 @@
       <c r="Z32" t="n">
         <v>109.4470925931567</v>
       </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>23423,29889</t>
-        </is>
+      <c r="AA32" t="n">
+        <v>23423.29889</v>
       </c>
     </row>
     <row r="33">
@@ -2635,10 +2573,8 @@
       <c r="Z33" t="n">
         <v>110.1584986950122</v>
       </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>23633,85279</t>
-        </is>
+      <c r="AA33" t="n">
+        <v>23633.85279</v>
       </c>
     </row>
     <row r="34">
@@ -2718,10 +2654,8 @@
       <c r="Z34" t="n">
         <v>110.8855447863993</v>
       </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>24945,70229</t>
-        </is>
+      <c r="AA34" t="n">
+        <v>24945.70229</v>
       </c>
     </row>
     <row r="35">
@@ -2799,10 +2733,8 @@
       <c r="Z35" t="n">
         <v>111.6063008275108</v>
       </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>26443,4314</t>
-        </is>
+      <c r="AA35" t="n">
+        <v>26443.4314</v>
       </c>
     </row>
     <row r="36">
@@ -2880,10 +2812,8 @@
       <c r="Z36" t="n">
         <v>112.3317417828897</v>
       </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>27142,53614</t>
-        </is>
+      <c r="AA36" t="n">
+        <v>27142.53614</v>
       </c>
     </row>
     <row r="37">
@@ -2963,10 +2893,8 @@
       <c r="Z37" t="n">
         <v>113.0618981044784</v>
       </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>28563,77497</t>
-        </is>
+      <c r="AA37" t="n">
+        <v>28563.77497</v>
       </c>
     </row>
     <row r="38">
@@ -3044,10 +2972,8 @@
       <c r="Z38" t="n">
         <v>113.7968004421575</v>
       </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>29676,58523</t>
-        </is>
+      <c r="AA38" t="n">
+        <v>29676.58523</v>
       </c>
     </row>
     <row r="39">
@@ -3125,10 +3051,8 @@
       <c r="Z39" t="n">
         <v>114.5478593250758</v>
       </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>30571,4393</t>
-        </is>
+      <c r="AA39" t="n">
+        <v>30571.4393</v>
       </c>
     </row>
     <row r="40">
@@ -3208,10 +3132,8 @@
       <c r="Z40" t="n">
         <v>115.3038751966212</v>
       </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>30832,98673</t>
-        </is>
+      <c r="AA40" t="n">
+        <v>30832.98673</v>
       </c>
     </row>
     <row r="41">
@@ -3289,10 +3211,8 @@
       <c r="Z41" t="n">
         <v>116.0187592228403</v>
       </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>31377,46595</t>
-        </is>
+      <c r="AA41" t="n">
+        <v>31377.46595</v>
       </c>
     </row>
     <row r="42">
@@ -3370,10 +3290,8 @@
       <c r="Z42" t="n">
         <v>116.7496774059442</v>
       </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>32130,85412</t>
-        </is>
+      <c r="AA42" t="n">
+        <v>32130.85412</v>
       </c>
     </row>
     <row r="43">
@@ -3453,10 +3371,8 @@
       <c r="Z43" t="n">
         <v>117.4968753413422</v>
       </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>33260,11391</t>
-        </is>
+      <c r="AA43" t="n">
+        <v>33260.11391</v>
       </c>
     </row>
     <row r="44">
@@ -3534,10 +3450,8 @@
       <c r="Z44" t="n">
         <v>118.3311031562658</v>
       </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>33192,67086</t>
-        </is>
+      <c r="AA44" t="n">
+        <v>33192.67086</v>
       </c>
     </row>
     <row r="45">
@@ -3615,10 +3529,8 @@
       <c r="Z45" t="n">
         <v>119.2304195402534</v>
       </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>33870,39123</t>
-        </is>
+      <c r="AA45" t="n">
+        <v>33870.39123</v>
       </c>
     </row>
     <row r="46">
@@ -3698,10 +3610,8 @@
       <c r="Z46" t="n">
         <v>120.1246476868053</v>
       </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>35720,14014</t>
-        </is>
+      <c r="AA46" t="n">
+        <v>35720.14014</v>
       </c>
     </row>
     <row r="47">
@@ -3779,10 +3689,8 @@
       <c r="Z47" t="n">
         <v>121.0255825444564</v>
       </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>37286,13477</t>
-        </is>
+      <c r="AA47" t="n">
+        <v>37286.13477</v>
       </c>
     </row>
     <row r="48">
@@ -3860,10 +3768,8 @@
       <c r="Z48" t="n">
         <v>121.9332744135398</v>
       </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>38015,67113</t>
-        </is>
+      <c r="AA48" t="n">
+        <v>38015.67113</v>
       </c>
     </row>
     <row r="49">
@@ -3943,10 +3849,8 @@
       <c r="Z49" t="n">
         <v>122.8477739716413</v>
       </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>38899,01054</t>
-        </is>
+      <c r="AA49" t="n">
+        <v>38899.01054</v>
       </c>
     </row>
     <row r="50">
@@ -4024,10 +3928,8 @@
       <c r="Z50" t="n">
         <v>123.7814170538258</v>
       </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>38810,18311</t>
-        </is>
+      <c r="AA50" t="n">
+        <v>38810.18311</v>
       </c>
     </row>
     <row r="51">
@@ -4105,10 +4007,8 @@
       <c r="Z51" t="n">
         <v>124.7097776817295</v>
       </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>39168,78273</t>
-        </is>
+      <c r="AA51" t="n">
+        <v>39168.78273</v>
       </c>
     </row>
     <row r="52">
@@ -4188,10 +4088,8 @@
       <c r="Z52" t="n">
         <v>125.6451010143425</v>
       </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>39261,72253</t>
-        </is>
+      <c r="AA52" t="n">
+        <v>39261.72253</v>
       </c>
     </row>
     <row r="53">
@@ -4269,10 +4167,8 @@
       <c r="Z53" t="n">
         <v>126.5874392719501</v>
       </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>39799,62195</t>
-        </is>
+      <c r="AA53" t="n">
+        <v>39799.62195</v>
       </c>
     </row>
     <row r="54">
@@ -4350,10 +4246,8 @@
       <c r="Z54" t="n">
         <v>127.5241863225625</v>
       </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>40366,30803</t>
-        </is>
+      <c r="AA54" t="n">
+        <v>40366.30803</v>
       </c>
     </row>
     <row r="55">
@@ -4433,10 +4327,8 @@
       <c r="Z55" t="n">
         <v>128.4678653013495</v>
       </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>41492,27791</t>
-        </is>
+      <c r="AA55" t="n">
+        <v>41492.27791</v>
       </c>
     </row>
     <row r="56">
@@ -4514,10 +4406,8 @@
       <c r="Z56" t="n">
         <v>129.6369228755918</v>
       </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>40830,18459</t>
-        </is>
+      <c r="AA56" t="n">
+        <v>40830.18459</v>
       </c>
     </row>
     <row r="57">
@@ -4595,10 +4485,8 @@
       <c r="Z57" t="n">
         <v>130.8295825660472</v>
       </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>41537,5141</t>
-        </is>
+      <c r="AA57" t="n">
+        <v>41537.5141</v>
       </c>
     </row>
     <row r="58">
@@ -4678,10 +4566,8 @@
       <c r="Z58" t="n">
         <v>132.0332147256549</v>
       </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>43937,49957</t>
-        </is>
+      <c r="AA58" t="n">
+        <v>43937.49957</v>
       </c>
     </row>
     <row r="59">
@@ -4759,10 +4645,8 @@
       <c r="Z59" t="n">
         <v>133.2479203011309</v>
       </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>45267,44354</t>
-        </is>
+      <c r="AA59" t="n">
+        <v>45267.44354</v>
       </c>
     </row>
     <row r="60">
@@ -4840,10 +4724,8 @@
       <c r="Z60" t="n">
         <v>134.4738011679013</v>
       </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>46732,2736</t>
-        </is>
+      <c r="AA60" t="n">
+        <v>46732.2736</v>
       </c>
     </row>
     <row r="61">
@@ -4923,10 +4805,8 @@
       <c r="Z61" t="n">
         <v>135.7647496591132</v>
       </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>48114,85605</t>
-        </is>
+      <c r="AA61" t="n">
+        <v>48114.85605</v>
       </c>
     </row>
     <row r="62">
@@ -5004,10 +4884,8 @@
       <c r="Z62" t="n">
         <v>136.9866324060452</v>
       </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>48160,91471</t>
-        </is>
+      <c r="AA62" t="n">
+        <v>48160.91471</v>
       </c>
     </row>
     <row r="63">
@@ -5085,10 +4963,8 @@
       <c r="Z63" t="n">
         <v>138.2469094241808</v>
       </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>48040,83319</t>
-        </is>
+      <c r="AA63" t="n">
+        <v>48040.83319</v>
       </c>
     </row>
     <row r="64">
@@ -5168,10 +5044,8 @@
       <c r="Z64" t="n">
         <v>139.5464303727682</v>
       </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>48509,64461</t>
-        </is>
+      <c r="AA64" t="n">
+        <v>48509.64461</v>
       </c>
     </row>
     <row r="65">
@@ -5249,10 +5123,8 @@
       <c r="Z65" t="n">
         <v>140.8302575321976</v>
       </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>49242,47088</t>
-        </is>
+      <c r="AA65" t="n">
+        <v>49242.47088</v>
       </c>
     </row>
     <row r="66">
@@ -5330,10 +5202,8 @@
       <c r="Z66" t="n">
         <v>142.1258959014939</v>
       </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>49270,43507</t>
-        </is>
+      <c r="AA66" t="n">
+        <v>49270.43507</v>
       </c>
     </row>
     <row r="67">
@@ -5413,10 +5283,8 @@
       <c r="Z67" t="n">
         <v>143.4334541437876</v>
       </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>49484,27887</t>
-        </is>
+      <c r="AA67" t="n">
+        <v>49484.27887</v>
       </c>
     </row>
     <row r="68">
@@ -5494,10 +5362,8 @@
       <c r="Z68" t="n">
         <v>144.8391019943967</v>
       </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>48506,3547</t>
-        </is>
+      <c r="AA68" t="n">
+        <v>48506.3547</v>
       </c>
     </row>
     <row r="69">
@@ -5575,10 +5441,8 @@
       <c r="Z69" t="n">
         <v>146.2874930143407</v>
       </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>48046,59052</t>
-        </is>
+      <c r="AA69" t="n">
+        <v>48046.59052</v>
       </c>
     </row>
     <row r="70">
@@ -5658,10 +5522,8 @@
       <c r="Z70" t="n">
         <v>147.6918529472784</v>
       </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>49066,46098</t>
-        </is>
+      <c r="AA70" t="n">
+        <v>49066.46098</v>
       </c>
     </row>
     <row r="71">
@@ -5739,10 +5601,8 @@
       <c r="Z71" t="n">
         <v>149.0949255502775</v>
       </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>51032,17903</t>
-        </is>
+      <c r="AA71" t="n">
+        <v>51032.17903</v>
       </c>
     </row>
     <row r="72">
@@ -5820,10 +5680,8 @@
       <c r="Z72" t="n">
         <v>150.6007842983353</v>
       </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>52379,395</t>
-        </is>
+      <c r="AA72" t="n">
+        <v>52379.395</v>
       </c>
     </row>
     <row r="73">
@@ -5903,10 +5761,8 @@
       <c r="Z73" t="n">
         <v>152.0917320628888</v>
       </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>54248,88333</t>
-        </is>
+      <c r="AA73" t="n">
+        <v>54248.88333</v>
       </c>
     </row>
     <row r="74">
@@ -5984,10 +5840,8 @@
       <c r="Z74" t="n">
         <v>154.9662657988774</v>
       </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>54540,0399</t>
-        </is>
+      <c r="AA74" t="n">
+        <v>54540.0399</v>
       </c>
     </row>
     <row r="75">
@@ -6065,10 +5919,8 @@
       <c r="Z75" t="n">
         <v>156.6244048429254</v>
       </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>54908,50922</t>
-        </is>
+      <c r="AA75" t="n">
+        <v>54908.50922</v>
       </c>
     </row>
     <row r="76">
@@ -6148,10 +6000,8 @@
       <c r="Z76" t="n">
         <v>158.2532986532918</v>
       </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>55610,90387</t>
-        </is>
+      <c r="AA76" t="n">
+        <v>55610.90387</v>
       </c>
     </row>
     <row r="77">
@@ -6229,10 +6079,8 @@
       <c r="Z77" t="n">
         <v>159.899132959286</v>
       </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>56329,74805</t>
-        </is>
+      <c r="AA77" t="n">
+        <v>56329.74805</v>
       </c>
     </row>
     <row r="78">
@@ -6310,10 +6158,8 @@
       <c r="Z78" t="n">
         <v>161.5620839420626</v>
       </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>57324,94422</t>
-        </is>
+      <c r="AA78" t="n">
+        <v>57324.94422</v>
       </c>
     </row>
     <row r="79">
@@ -6393,10 +6239,8 @@
       <c r="Z79" t="n">
         <v>163.161548573089</v>
       </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>58137,55067</t>
-        </is>
+      <c r="AA79" t="n">
+        <v>58137.55067</v>
       </c>
     </row>
     <row r="80">
@@ -6474,10 +6318,8 @@
       <c r="Z80" t="n">
         <v>164.4505248068164</v>
       </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>57695,88097</t>
-        </is>
+      <c r="AA80" t="n">
+        <v>57695.88097</v>
       </c>
     </row>
     <row r="81">
@@ -6555,10 +6397,8 @@
       <c r="Z81" t="n">
         <v>165.7003487953482</v>
       </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>57930,28668</t>
-        </is>
+      <c r="AA81" t="n">
+        <v>57930.28668</v>
       </c>
     </row>
     <row r="82">
@@ -6638,10 +6478,8 @@
       <c r="Z82" t="n">
         <v>166.9762414810724</v>
       </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>59415,67864</t>
-        </is>
+      <c r="AA82" t="n">
+        <v>59415.67864</v>
       </c>
     </row>
     <row r="83">
@@ -6719,10 +6557,8 @@
       <c r="Z83" t="n">
         <v>168.2452609163286</v>
       </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>61332,04812</t>
-        </is>
+      <c r="AA83" t="n">
+        <v>61332.04812</v>
       </c>
     </row>
     <row r="84">
@@ -6800,10 +6636,8 @@
       <c r="Z84" t="n">
         <v>169.507100373201</v>
       </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>62605,24124</t>
-        </is>
+      <c r="AA84" t="n">
+        <v>62605.24124</v>
       </c>
     </row>
     <row r="85">
@@ -6883,10 +6717,8 @@
       <c r="Z85" t="n">
         <v>170.7784036260001</v>
       </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>63890,77149</t>
-        </is>
+      <c r="AA85" t="n">
+        <v>63890.77149</v>
       </c>
     </row>
     <row r="86">
@@ -6964,10 +6796,8 @@
       <c r="Z86" t="n">
         <v>172.0592416531951</v>
       </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>64700,08805</t>
-        </is>
+      <c r="AA86" t="n">
+        <v>64700.08805</v>
       </c>
     </row>
     <row r="87">
@@ -7045,10 +6875,8 @@
       <c r="Z87" t="n">
         <v>173.349685965594</v>
       </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>65157,3848</t>
-        </is>
+      <c r="AA87" t="n">
+        <v>65157.3848</v>
       </c>
     </row>
     <row r="88">
@@ -25074,7 +24902,7 @@
         <v>430.2324853143676</v>
       </c>
       <c r="N312" t="n">
-        <v>1015226501</v>
+        <v>1015226812</v>
       </c>
       <c r="O312" t="n">
         <v>5.3338</v>
@@ -25101,7 +24929,7 @@
       <c r="W312" t="inlineStr"/>
       <c r="X312" t="inlineStr"/>
       <c r="Y312" t="n">
-        <v>730814</v>
+        <v>730831</v>
       </c>
       <c r="Z312" t="n">
         <v>763.9656954694356</v>
@@ -25147,7 +24975,7 @@
         <v>432.2976012438765</v>
       </c>
       <c r="N313" t="n">
-        <v>1028404727</v>
+        <v>1028405038</v>
       </c>
       <c r="O313" t="n">
         <v>5.5024</v>
@@ -25174,7 +25002,7 @@
       <c r="W313" t="inlineStr"/>
       <c r="X313" t="inlineStr"/>
       <c r="Y313" t="n">
-        <v>733664</v>
+        <v>735358</v>
       </c>
       <c r="Z313" t="n">
         <v>767.7091273772357</v>
@@ -25218,7 +25046,7 @@
         <v>435.9289010943251</v>
       </c>
       <c r="N314" t="n">
-        <v>1017280764</v>
+        <v>1011399128</v>
       </c>
       <c r="O314" t="n">
         <v>5.2301</v>
@@ -25245,7 +25073,7 @@
       <c r="W314" t="inlineStr"/>
       <c r="X314" t="inlineStr"/>
       <c r="Y314" t="n">
-        <v>742581</v>
+        <v>746553</v>
       </c>
       <c r="Z314" t="n">
         <v>771.4709021013841</v>
@@ -25288,7 +25116,9 @@
       <c r="M315" t="n">
         <v>438.9804034019853</v>
       </c>
-      <c r="N315" t="inlineStr"/>
+      <c r="N315" t="n">
+        <v>1010620456</v>
+      </c>
       <c r="O315" t="n">
         <v>5.1495</v>
       </c>
@@ -25313,11 +25143,15 @@
       </c>
       <c r="W315" t="inlineStr"/>
       <c r="X315" t="inlineStr"/>
-      <c r="Y315" t="inlineStr"/>
+      <c r="Y315" t="n">
+        <v>756975</v>
+      </c>
       <c r="Z315" t="n">
         <v>775.2511095216809</v>
       </c>
-      <c r="AA315" t="inlineStr"/>
+      <c r="AA315" t="n">
+        <v>687639</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -25340,7 +25174,7 @@
       <c r="N316" t="inlineStr"/>
       <c r="O316" t="inlineStr"/>
       <c r="P316" t="n">
-        <v>14.83</v>
+        <v>14.81</v>
       </c>
       <c r="Q316" t="inlineStr"/>
       <c r="R316" t="inlineStr"/>
